--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/td/PycharmProjects/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56EA14A-4595-F040-822C-8FF4A1E80F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14FE762-6AF7-814F-BC64-75959BABEE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -498,18 +498,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -814,22 +815,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T24"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="81.5" customWidth="1"/>
+    <col min="3" max="3" width="59.83203125" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.33203125" customWidth="1"/>
     <col min="8" max="8" width="43.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="53.6640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="72.1640625" bestFit="1" customWidth="1"/>
@@ -897,31 +898,31 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="I2" s="8"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="O2" s="5" t="s">
+      <c r="I2" s="6"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="O2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -947,19 +948,19 @@
       <c r="H3" t="s">
         <v>102</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="7">
         <v>973000</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="7">
         <v>100000</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="7">
         <v>973000</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="8">
         <v>294728</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="7">
         <v>10000000</v>
       </c>
       <c r="O3" t="s">
@@ -982,11 +983,11 @@
       <c r="D4" t="s">
         <v>120</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="3"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -1010,17 +1011,17 @@
       <c r="H5" t="s">
         <v>108</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="7">
         <v>875000</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="7">
         <v>500000</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="7">
         <v>875000</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3">
+      <c r="L5" s="7"/>
+      <c r="M5" s="7">
         <v>1200000</v>
       </c>
       <c r="O5" t="s">
@@ -1058,7 +1059,11 @@
       <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="3"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -1079,20 +1084,20 @@
       <c r="F7" t="s">
         <v>118</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>2017</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="7">
         <v>75000</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3">
+      <c r="J7" s="7"/>
+      <c r="K7" s="7">
         <v>133685</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="7">
         <v>75000</v>
       </c>
-      <c r="M7" s="3"/>
+      <c r="M7" s="7"/>
       <c r="O7" t="s">
         <v>28</v>
       </c>
@@ -1112,31 +1117,31 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="8"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="O8" s="5" t="s">
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="O8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Q8" s="5" t="s">
+      <c r="Q8" s="3" t="s">
         <v>107</v>
       </c>
     </row>
@@ -1162,17 +1167,17 @@
       <c r="G9">
         <v>2018</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="7">
         <v>3677</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="7">
         <v>1710</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2">
+      <c r="K9" s="7"/>
+      <c r="L9" s="7">
         <v>3677</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="7">
         <v>5623</v>
       </c>
       <c r="O9" t="s">
@@ -1201,15 +1206,15 @@
       <c r="F10" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="7">
         <v>60.37</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2">
+      <c r="J10" s="7"/>
+      <c r="K10" s="7">
         <v>60.37</v>
       </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
       <c r="O10" t="s">
         <v>28</v>
       </c>
@@ -1242,15 +1247,15 @@
       <c r="F11" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="7">
         <v>0.61</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="7">
         <v>0.61</v>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11">
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7">
         <v>0.71</v>
       </c>
       <c r="O11" t="s">
@@ -1291,20 +1296,20 @@
       <c r="G12">
         <v>2011</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="7">
         <v>11</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="7">
         <v>11</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="7">
         <v>33</v>
       </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
       <c r="O12" t="s">
         <v>28</v>
       </c>
@@ -1334,15 +1339,15 @@
       <c r="F13" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="7">
         <v>4.9400000000000004</v>
       </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2">
+      <c r="J13" s="7"/>
+      <c r="K13" s="7">
         <v>4.9400000000000004</v>
       </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
       <c r="O13" t="s">
         <v>28</v>
       </c>
@@ -1378,13 +1383,13 @@
       <c r="H14" t="s">
         <v>65</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="7">
         <v>99.44</v>
       </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
       <c r="O14" t="s">
         <v>28</v>
       </c>
@@ -1411,15 +1416,15 @@
       <c r="G15">
         <v>2022</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="7">
         <v>11</v>
       </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2">
+      <c r="J15" s="7"/>
+      <c r="K15" s="7">
         <v>11</v>
       </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
       <c r="O15" t="s">
         <v>28</v>
       </c>
@@ -1455,15 +1460,15 @@
       <c r="H16" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="7">
         <v>249634</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="7">
         <v>178920</v>
       </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16">
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7">
         <v>249634</v>
       </c>
       <c r="O16" t="s">
@@ -1498,15 +1503,15 @@
       <c r="G17">
         <v>2017</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="7">
         <v>130</v>
       </c>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2">
+      <c r="J17" s="7"/>
+      <c r="K17" s="7">
         <v>130</v>
       </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
       <c r="O17" t="s">
         <v>21</v>
       </c>
@@ -1542,20 +1547,20 @@
       <c r="G18">
         <v>2015</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="7">
         <v>50</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="7">
         <v>25</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="7">
         <v>50</v>
       </c>
-      <c r="L18" s="2"/>
-      <c r="M18">
+      <c r="L18" s="7"/>
+      <c r="M18" s="7">
         <v>100</v>
       </c>
       <c r="O18" t="s">
@@ -1590,15 +1595,15 @@
       <c r="G19">
         <v>2018</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="7">
         <v>300</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="7">
         <v>200</v>
       </c>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19">
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7">
         <v>400</v>
       </c>
       <c r="O19" t="s">
@@ -1636,18 +1641,18 @@
       <c r="G20">
         <v>2018</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="7">
         <v>448677628</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="7">
         <v>448677628</v>
       </c>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
       <c r="O20" t="s">
         <v>28</v>
       </c>
@@ -1677,13 +1682,13 @@
       <c r="G21">
         <v>2018</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="7">
         <v>33945</v>
       </c>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
@@ -1704,9 +1709,13 @@
       <c r="G22">
         <v>2018</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="7">
         <v>5171000</v>
       </c>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
@@ -1715,7 +1724,7 @@
       <c r="B23" t="s">
         <v>96</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="5" t="s">
         <v>130</v>
       </c>
       <c r="E23" t="s">
@@ -1727,12 +1736,34 @@
       <c r="G23">
         <v>2018</v>
       </c>
-      <c r="I23" s="3">
+      <c r="I23" s="7">
         <v>100000</v>
       </c>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="I24" s="3"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/td/PycharmProjects/CCJ/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56EA14A-4595-F040-822C-8FF4A1E80F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F644ED30-C8C0-F946-A689-9B96AB765409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,7 +438,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
@@ -498,7 +499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -510,6 +511,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1456,15 +1458,12 @@
         <v>73</v>
       </c>
       <c r="I16" s="3">
-        <v>249634</v>
-      </c>
-      <c r="J16">
-        <v>178920</v>
+        <v>295275</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
-      <c r="M16">
-        <v>249634</v>
+      <c r="M16" s="9">
+        <v>295275</v>
       </c>
       <c r="O16" t="s">
         <v>28</v>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F644ED30-C8C0-F946-A689-9B96AB765409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D58EDB7-4D33-C848-8F92-2012F1D42561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,9 +179,6 @@
     <t>Bureau of Justice Statistics</t>
   </si>
   <si>
-    <t>https://bjs.ojp.gov/employment-state-and-federal-prisoners-prior-incarceration-2016?utm_source=chatgpt.com</t>
-  </si>
-  <si>
     <t>Bureau of Justice Statistics Special Report Profile of Jail Inmates, 2002</t>
   </si>
   <si>
@@ -305,9 +302,6 @@
     <t>NEJM</t>
   </si>
   <si>
-    <t>https://www.nejm.org/doi/full/10.1056/NEJMsa064115?utm_source=chatgpt.com</t>
-  </si>
-  <si>
     <t>ccj_funding_2018</t>
   </si>
   <si>
@@ -317,9 +311,6 @@
     <t>dollars per year</t>
   </si>
   <si>
-    <t>https://cook-dashboard.loyolaccj.org/jail/admissions?utm_source=chatgpt.com</t>
-  </si>
-  <si>
     <t>n_detainees</t>
   </si>
   <si>
@@ -432,6 +423,15 @@
   </si>
   <si>
     <t>needed to divide it with annual running detainee population</t>
+  </si>
+  <si>
+    <t>https://bjs.ojp.gov/employment-state-and-federal-prisoners-prior-incarceration-2016</t>
+  </si>
+  <si>
+    <t>https://www.nejm.org/doi/full/10.1056/NEJMsa064115</t>
+  </si>
+  <si>
+    <t>https://cook-dashboard.loyolaccj.org/jail/admissions</t>
   </si>
 </sst>
 </file>
@@ -442,7 +442,7 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,6 +478,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -496,10 +504,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -512,8 +521,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -857,16 +868,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>7</v>
@@ -916,7 +927,7 @@
         <v>20</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I2" s="8"/>
       <c r="J2" s="6"/>
@@ -941,13 +952,13 @@
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F3" t="s">
         <v>35</v>
       </c>
       <c r="H3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I3" s="3">
         <v>973000</v>
@@ -968,21 +979,21 @@
         <v>21</v>
       </c>
       <c r="R3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
       </c>
       <c r="C4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" t="s">
         <v>117</v>
-      </c>
-      <c r="D4" t="s">
-        <v>120</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -998,19 +1009,19 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D5">
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F5" t="s">
         <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I5" s="3">
         <v>875000</v>
@@ -1029,33 +1040,33 @@
         <v>21</v>
       </c>
       <c r="P5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="R5" t="s">
         <v>25</v>
       </c>
       <c r="S5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -1070,16 +1081,16 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G7" s="3">
         <v>2017</v>
@@ -1099,19 +1110,19 @@
         <v>28</v>
       </c>
       <c r="P7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="Q7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="R7" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="S7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.2">
@@ -1139,7 +1150,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
@@ -1156,7 +1167,7 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F9" t="s">
         <v>35</v>
@@ -1261,31 +1272,31 @@
       <c r="Q11" t="s">
         <v>47</v>
       </c>
-      <c r="R11" t="s">
+      <c r="R11" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="S11" t="s">
         <v>48</v>
       </c>
-      <c r="S11" t="s">
+      <c r="T11" t="s">
         <v>49</v>
-      </c>
-      <c r="T11" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
         <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
         <v>40</v>
       </c>
       <c r="E12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s">
         <v>35</v>
@@ -1294,7 +1305,7 @@
         <v>2011</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I12" s="3">
         <v>11</v>
@@ -1311,27 +1322,27 @@
         <v>28</v>
       </c>
       <c r="Q12" t="s">
+        <v>53</v>
+      </c>
+      <c r="R12" t="s">
         <v>54</v>
-      </c>
-      <c r="R12" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
         <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
         <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" t="s">
         <v>35</v>
@@ -1349,36 +1360,36 @@
         <v>28</v>
       </c>
       <c r="P13" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q13" t="s">
         <v>59</v>
       </c>
-      <c r="Q13" t="s">
+      <c r="R13" t="s">
         <v>60</v>
-      </c>
-      <c r="R13" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
         <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s">
         <v>35</v>
       </c>
       <c r="H14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I14" s="3">
         <v>99.44</v>
@@ -1393,19 +1404,19 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>38</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s">
         <v>35</v>
@@ -1426,27 +1437,27 @@
         <v>28</v>
       </c>
       <c r="Q15" t="s">
+        <v>67</v>
+      </c>
+      <c r="R15" t="s">
         <v>68</v>
-      </c>
-      <c r="R15" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
         <v>38</v>
       </c>
       <c r="C16" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" t="s">
         <v>71</v>
       </c>
-      <c r="D16" t="s">
-        <v>72</v>
-      </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s">
         <v>35</v>
@@ -1455,7 +1466,7 @@
         <v>2021</v>
       </c>
       <c r="H16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I16" s="3">
         <v>295275</v>
@@ -1469,30 +1480,30 @@
         <v>28</v>
       </c>
       <c r="Q16" t="s">
+        <v>67</v>
+      </c>
+      <c r="R16" t="s">
         <v>68</v>
-      </c>
-      <c r="R16" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" t="s">
         <v>74</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>76</v>
       </c>
       <c r="D17" t="s">
         <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G17">
         <v>2017</v>
@@ -1510,39 +1521,39 @@
         <v>21</v>
       </c>
       <c r="P17" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q17" t="s">
         <v>77</v>
       </c>
-      <c r="Q17" t="s">
+      <c r="R17" t="s">
         <v>78</v>
-      </c>
-      <c r="R17" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
         <v>80</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>81</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>82</v>
       </c>
-      <c r="D18" t="s">
-        <v>83</v>
-      </c>
       <c r="E18" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F18" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G18">
         <v>2015</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I18" s="3">
         <v>50</v>
@@ -1561,30 +1572,30 @@
         <v>28</v>
       </c>
       <c r="Q18" t="s">
+        <v>83</v>
+      </c>
+      <c r="R18" t="s">
         <v>84</v>
-      </c>
-      <c r="R18" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
         <v>86</v>
       </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
       <c r="D19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G19">
         <v>2018</v>
@@ -1604,39 +1615,39 @@
         <v>28</v>
       </c>
       <c r="P19" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q19" t="s">
         <v>88</v>
       </c>
-      <c r="Q19" t="s">
-        <v>89</v>
-      </c>
-      <c r="R19" t="s">
-        <v>90</v>
+      <c r="R19" s="10" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G20">
         <v>2018</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I20" s="3">
         <v>448677628</v>
@@ -1653,25 +1664,25 @@
       <c r="Q20" t="s">
         <v>43</v>
       </c>
-      <c r="R20" t="s">
-        <v>94</v>
+      <c r="R20" s="10" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" t="s">
         <v>95</v>
       </c>
-      <c r="B21" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="E21" t="s">
-        <v>98</v>
-      </c>
       <c r="F21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G21">
         <v>2018</v>
@@ -1686,19 +1697,19 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F22" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G22">
         <v>2018</v>
@@ -1709,19 +1720,19 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E23" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G23">
         <v>2018</v>
@@ -1734,6 +1745,11 @@
       <c r="I24" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="R20" r:id="rId1" xr:uid="{4F8FD284-A023-164D-8A61-F651B098BF3F}"/>
+    <hyperlink ref="R19" r:id="rId2" xr:uid="{913DD2C2-09D4-6340-B25B-D342990A3AE8}"/>
+    <hyperlink ref="R11" r:id="rId3" xr:uid="{C43FA892-8D61-5549-A0D1-6272414542B3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D58EDB7-4D33-C848-8F92-2012F1D42561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6FFDD5-4077-F84B-A151-D564D9BD031D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="134">
   <si>
     <t>row_var</t>
   </si>
@@ -431,7 +431,10 @@
     <t>https://www.nejm.org/doi/full/10.1056/NEJMsa064115</t>
   </si>
   <si>
-    <t>https://cook-dashboard.loyolaccj.org/jail/admissions</t>
+    <t>chrome-extension://efaidnbmnnnibpcajpcglclefindmkaj/https://opendocs.cookcountyil.gov/budget/archive/2018_Annual_Appropriation_Volume_2.pdf</t>
+  </si>
+  <si>
+    <t>2018 Annual Appropriations</t>
   </si>
 </sst>
 </file>
@@ -1662,7 +1665,7 @@
         <v>28</v>
       </c>
       <c r="Q20" t="s">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="R20" s="10" t="s">
         <v>132</v>
@@ -1746,9 +1749,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="R20" r:id="rId1" xr:uid="{4F8FD284-A023-164D-8A61-F651B098BF3F}"/>
-    <hyperlink ref="R19" r:id="rId2" xr:uid="{913DD2C2-09D4-6340-B25B-D342990A3AE8}"/>
-    <hyperlink ref="R11" r:id="rId3" xr:uid="{C43FA892-8D61-5549-A0D1-6272414542B3}"/>
+    <hyperlink ref="R19" r:id="rId1" xr:uid="{913DD2C2-09D4-6340-B25B-D342990A3AE8}"/>
+    <hyperlink ref="R11" r:id="rId2" xr:uid="{C43FA892-8D61-5549-A0D1-6272414542B3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6FFDD5-4077-F84B-A151-D564D9BD031D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C48CF0-F7BB-D04C-8450-C9EF00E4D4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="132">
   <si>
     <t>row_var</t>
   </si>
@@ -414,12 +414,6 @@
   </si>
   <si>
     <t>dollar per victim</t>
-  </si>
-  <si>
-    <t>n of all Detainees in 2018</t>
-  </si>
-  <si>
-    <t>n_jail_flow</t>
   </si>
   <si>
     <t>needed to divide it with annual running detainee population</t>
@@ -1276,7 +1270,7 @@
         <v>47</v>
       </c>
       <c r="R11" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="S11" t="s">
         <v>48</v>
@@ -1624,7 +1618,7 @@
         <v>88</v>
       </c>
       <c r="R19" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
@@ -1650,7 +1644,7 @@
         <v>2018</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I20" s="3">
         <v>448677628</v>
@@ -1665,10 +1659,10 @@
         <v>28</v>
       </c>
       <c r="Q20" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="R20" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
@@ -1722,27 +1716,7 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>128</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>127</v>
-      </c>
-      <c r="E23" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" t="s">
-        <v>115</v>
-      </c>
-      <c r="G23">
-        <v>2018</v>
-      </c>
-      <c r="I23" s="3">
-        <v>100000</v>
-      </c>
+      <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="I24" s="3"/>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/td/PycharmProjects/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B14FE762-6AF7-814F-BC64-75959BABEE02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B86A90-B744-F845-96BC-38C1D13BB9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -441,7 +441,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,6 +477,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -495,10 +503,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -511,8 +520,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -825,7 +836,7 @@
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.33203125" customWidth="1"/>
-    <col min="8" max="8" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" customWidth="1"/>
     <col min="9" max="9" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
@@ -948,8 +959,8 @@
       <c r="H3" t="s">
         <v>102</v>
       </c>
-      <c r="I3" s="7">
-        <v>973000</v>
+      <c r="I3" s="8">
+        <v>294728</v>
       </c>
       <c r="J3" s="7">
         <v>100000</v>
@@ -966,7 +977,7 @@
       <c r="O3" t="s">
         <v>21</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="10" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1012,17 +1023,17 @@
         <v>108</v>
       </c>
       <c r="I5" s="7">
-        <v>875000</v>
+        <v>16785</v>
       </c>
       <c r="J5" s="7">
-        <v>500000</v>
+        <v>9377</v>
       </c>
       <c r="K5" s="7">
-        <v>875000</v>
+        <v>16785</v>
       </c>
       <c r="L5" s="7"/>
       <c r="M5" s="7">
-        <v>1200000</v>
+        <v>37518</v>
       </c>
       <c r="O5" t="s">
         <v>21</v>
@@ -1107,13 +1118,13 @@
       <c r="Q7" t="s">
         <v>111</v>
       </c>
-      <c r="R7" t="s">
+      <c r="R7" s="10" t="s">
         <v>112</v>
       </c>
       <c r="S7" t="s">
         <v>113</v>
       </c>
-      <c r="T7" t="s">
+      <c r="T7" s="10" t="s">
         <v>109</v>
       </c>
     </row>
@@ -1766,6 +1777,11 @@
       <c r="M26" s="7"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="R7" r:id="rId1" xr:uid="{DB52D8D2-D913-6047-A2C0-C19889E9CABC}"/>
+    <hyperlink ref="T7" r:id="rId2" xr:uid="{99E21AE3-A092-4248-BD86-FB2A04B383D0}"/>
+    <hyperlink ref="R3" r:id="rId3" xr:uid="{59664F8A-ED6E-714E-A53D-A9C25DDCDE66}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/td/PycharmProjects/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B86A90-B744-F845-96BC-38C1D13BB9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{019B570E-A235-BA4C-AF7E-343493279F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="148">
   <si>
     <t>row_var</t>
   </si>
@@ -432,6 +432,51 @@
   </si>
   <si>
     <t>needed to divide it with annual running detainee population</t>
+  </si>
+  <si>
+    <t>value bail as crime reduction and quantify the possibility of murder vs death in detainment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes: assume a range for the value to society, and take into consideration those who do not been offered bail inlcudes the failure to appear at court. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">how to prevent victimization  - how to map it to how much crime is prevented by pretrial detention. Benefits of pretrial detention as preventing crimes.  Add more context </t>
+  </si>
+  <si>
+    <t>random judge assignment - whats the recidivism impact of pretrial detention</t>
+  </si>
+  <si>
+    <t>police statistics - how can accurately measure prevented crimes</t>
+  </si>
+  <si>
+    <t>Granularity vs disaggregation to address policy levers?</t>
+  </si>
+  <si>
+    <t>use disciplinary measures and detainee victimization from the CCJ dataset - how to use infringements and incidents to measure them?</t>
+  </si>
+  <si>
+    <t>Should we measure experiential aspects like access to phone, etc?</t>
+  </si>
+  <si>
+    <t>Get extreme outcomes - solitary, extreme health, etc.. Highlight the edge MVPF values</t>
+  </si>
+  <si>
+    <t>Get health outcomes from movement data, solitary and electronic monitoring</t>
+  </si>
+  <si>
+    <t>other meaningful evalutaion from the dataset?</t>
+  </si>
+  <si>
+    <t>Scenarios: use the extreme situations for that!</t>
+  </si>
+  <si>
+    <t>GET LITERATURE</t>
+  </si>
+  <si>
+    <t>Explore where the general measures are not making sense - where evaluation makes more sense than wtp</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/33033154/</t>
   </si>
 </sst>
 </file>
@@ -826,12 +871,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="59.83203125" customWidth="1"/>
+    <col min="3" max="3" width="88.83203125" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
@@ -850,7 +895,7 @@
     <col min="20" max="20" width="102.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -909,7 +954,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>16</v>
       </c>
@@ -937,7 +982,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -980,8 +1025,11 @@
       <c r="R3" s="10" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U3" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>123</v>
       </c>
@@ -999,8 +1047,11 @@
       <c r="K4" s="7"/>
       <c r="L4" s="8"/>
       <c r="M4" s="7"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U4" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1053,8 +1104,11 @@
       <c r="T5" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U5" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>122</v>
       </c>
@@ -1075,8 +1129,11 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U6" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1127,15 +1184,18 @@
       <c r="T7" s="10" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="U7" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -1155,8 +1215,11 @@
       <c r="Q8" s="3" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1198,7 +1261,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1239,7 +1302,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -1285,7 +1348,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>51</v>
       </c>
@@ -1331,7 +1394,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>56</v>
       </c>
@@ -1372,7 +1435,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -1405,7 +1468,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -1446,7 +1509,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -1763,6 +1826,9 @@
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C25" s="5" t="s">
+        <v>138</v>
+      </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
@@ -1770,11 +1836,49 @@
       <c r="M25" s="7"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C26" s="5" t="s">
+        <v>139</v>
+      </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
       <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C27" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C28" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C29" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C30" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C31" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C33" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C34" s="5" t="s">
+        <v>146</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -1,19 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C48CF0-F7BB-D04C-8450-C9EF00E4D4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F70A88-DBF9-3945-B82D-C887358E98FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Baseline components " sheetId="4" r:id="rId1"/>
+    <sheet name="MVPF calculation" sheetId="2" r:id="rId2"/>
+    <sheet name="CCJ Subset Quantification" sheetId="3" r:id="rId3"/>
+    <sheet name="OLD Baseline components" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="149">
   <si>
     <t>row_var</t>
   </si>
@@ -429,6 +432,57 @@
   </si>
   <si>
     <t>2018 Annual Appropriations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">formula </t>
+  </si>
+  <si>
+    <t>Min alternative</t>
+  </si>
+  <si>
+    <t>Max alternative</t>
+  </si>
+  <si>
+    <t>Value to society</t>
+  </si>
+  <si>
+    <t>Value to detainee</t>
+  </si>
+  <si>
+    <t>Cost to government</t>
+  </si>
+  <si>
+    <t>dollars per detainee</t>
+  </si>
+  <si>
+    <t>min_alternative</t>
+  </si>
+  <si>
+    <t>max_alternative</t>
+  </si>
+  <si>
+    <t>nudge_court_appear</t>
+  </si>
+  <si>
+    <t>Valuation of effects of detention on court appearance</t>
+  </si>
+  <si>
+    <t>crime type</t>
+  </si>
+  <si>
+    <t>Relative Harm Valuation (RHV)</t>
+  </si>
+  <si>
+    <t>baseline (1) /alternative</t>
+  </si>
+  <si>
+    <t>Incapacitation and deterrance crime effects of detention, valued by RHV</t>
+  </si>
+  <si>
+    <t>Wrongful death damages Social cost of detainment (remove wtp for a human life)</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -484,12 +538,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -505,7 +565,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -519,6 +579,10 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -823,6 +887,776 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{018C5E1B-70FC-CE48-BD0C-84D5CA275194}">
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" customWidth="1"/>
+    <col min="12" max="12" width="53.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="72.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="138.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="54.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="102.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="14">
+        <v>1</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I4" s="3">
+        <v>973000</v>
+      </c>
+      <c r="J4" s="3">
+        <v>100000</v>
+      </c>
+      <c r="K4" s="3">
+        <v>10000000</v>
+      </c>
+      <c r="N4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>2022</v>
+      </c>
+      <c r="I5" s="3">
+        <v>11</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="M5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6">
+        <v>2021</v>
+      </c>
+      <c r="H6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I6" s="3">
+        <v>295275</v>
+      </c>
+      <c r="K6" s="9">
+        <v>295275</v>
+      </c>
+      <c r="M6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" t="s">
+        <v>115</v>
+      </c>
+      <c r="G7">
+        <v>2018</v>
+      </c>
+      <c r="I7" s="3">
+        <v>300</v>
+      </c>
+      <c r="J7">
+        <v>200</v>
+      </c>
+      <c r="K7">
+        <v>400</v>
+      </c>
+      <c r="L7" t="s">
+        <v>87</v>
+      </c>
+      <c r="M7" t="s">
+        <v>88</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8">
+        <v>2018</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="3">
+        <v>448677628</v>
+      </c>
+      <c r="J8">
+        <v>448677628</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="M8" t="s">
+        <v>131</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" t="s">
+        <v>148</v>
+      </c>
+      <c r="G9">
+        <v>2018</v>
+      </c>
+      <c r="I9" s="3">
+        <v>33945</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" t="s">
+        <v>148</v>
+      </c>
+      <c r="G10">
+        <v>2018</v>
+      </c>
+      <c r="I10" s="3">
+        <v>5171000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" t="s">
+        <v>148</v>
+      </c>
+      <c r="G12" t="s">
+        <v>148</v>
+      </c>
+      <c r="I12" s="3">
+        <v>70</v>
+      </c>
+      <c r="J12" s="2">
+        <v>60.37</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" t="s">
+        <v>42</v>
+      </c>
+      <c r="M12" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="N7" r:id="rId1" xr:uid="{126C1809-D3C8-9244-9EA2-45648641ED16}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CCEB78A-8117-3143-B4E8-94B34C4CEAC6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EF59096-85EC-6844-83BB-A3D9FC91749B}">
+  <dimension ref="A1:S8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="12"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="P2" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3">
+        <v>2018</v>
+      </c>
+      <c r="I3" s="3">
+        <v>3677</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1710</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2">
+        <v>3677</v>
+      </c>
+      <c r="M3" s="2">
+        <v>5623</v>
+      </c>
+      <c r="P3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0.61</v>
+      </c>
+      <c r="J4">
+        <v>0.61</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4">
+        <v>0.71</v>
+      </c>
+      <c r="P4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q4" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="R4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5">
+        <v>2011</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="I5" s="3">
+        <v>11</v>
+      </c>
+      <c r="J5">
+        <v>11</v>
+      </c>
+      <c r="K5" s="2">
+        <v>33</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="P5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="3">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="O6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P6" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="3">
+        <v>99.44</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>125</v>
+      </c>
+      <c r="F8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8">
+        <v>2017</v>
+      </c>
+      <c r="I8" s="3">
+        <v>130</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2">
+        <v>130</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="O8" t="s">
+        <v>76</v>
+      </c>
+      <c r="P8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="Q4" r:id="rId1" xr:uid="{E2688716-666A-5E4E-A84E-AC0F91173F0E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1052,24 +1886,6 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3"/>
-    </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
@@ -1192,47 +2008,6 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="3">
-        <v>60.37</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2">
-        <v>60.37</v>
-      </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="O10" t="s">
-        <v>28</v>
-      </c>
-      <c r="P10" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>43</v>
-      </c>
-      <c r="R10" t="s">
-        <v>44</v>
-      </c>
-    </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>45</v>
@@ -1716,10 +2491,63 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="I24" s="3"/>
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="3">
+        <v>60.37</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2">
+        <v>60.37</v>
+      </c>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="O24" t="s">
+        <v>28</v>
+      </c>
+      <c r="P24" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>43</v>
+      </c>
+      <c r="R24" t="s">
+        <v>44</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F70A88-DBF9-3945-B82D-C887358E98FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A49AAD6-7B03-CF42-9CDD-DED41A7C8B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3200" yWindow="760" windowWidth="26200" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline components " sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="151">
   <si>
     <t>row_var</t>
   </si>
@@ -434,9 +434,6 @@
     <t>2018 Annual Appropriations</t>
   </si>
   <si>
-    <t xml:space="preserve">formula </t>
-  </si>
-  <si>
     <t>Min alternative</t>
   </si>
   <si>
@@ -483,6 +480,15 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>Numerator Additive component Name</t>
+  </si>
+  <si>
+    <t>component value</t>
+  </si>
+  <si>
+    <t>Denominator Additive component Name</t>
   </si>
 </sst>
 </file>
@@ -565,7 +571,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -579,10 +585,9 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -920,7 +925,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -938,10 +943,10 @@
         <v>111</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>11</v>
@@ -959,40 +964,46 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="13">
+        <v>2020</v>
+      </c>
+      <c r="H2" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="14">
-        <v>1</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+      <c r="I2" s="13">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="14">
+      <c r="B3" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="11">
         <v>1</v>
       </c>
     </row>
@@ -1001,16 +1012,16 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F4" t="s">
         <v>35</v>
@@ -1036,7 +1047,7 @@
         <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C5" t="s">
         <v>66</v>
@@ -1070,10 +1081,10 @@
         <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1108,7 +1119,7 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
         <v>86</v>
@@ -1149,7 +1160,7 @@
         <v>89</v>
       </c>
       <c r="B8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
         <v>90</v>
@@ -1198,7 +1209,7 @@
         <v>95</v>
       </c>
       <c r="F9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G9">
         <v>2018</v>
@@ -1226,7 +1237,7 @@
         <v>95</v>
       </c>
       <c r="F10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G10">
         <v>2018</v>
@@ -1252,10 +1263,10 @@
         <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I11" s="3">
         <v>0.7</v>
@@ -1278,10 +1289,10 @@
         <v>41</v>
       </c>
       <c r="F12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G12" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I12" s="3">
         <v>70</v>
@@ -1310,12 +1321,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CCEB78A-8117-3143-B4E8-94B34C4CEAC6}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="31.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>132</v>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1362,7 +1388,7 @@
         <v>111</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
@@ -1371,7 +1397,7 @@
         <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>11</v>
@@ -1389,28 +1415,28 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="P2" s="11" t="s">
+      <c r="I2" s="3"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="P2" t="s">
         <v>104</v>
       </c>
     </row>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A49AAD6-7B03-CF42-9CDD-DED41A7C8B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AF519A-1F2D-6B49-8894-C1E5E179B313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3200" yWindow="760" windowWidth="26200" windowHeight="14500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2140" yWindow="-27360" windowWidth="32280" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline components " sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="151">
   <si>
     <t>row_var</t>
   </si>
@@ -473,9 +473,6 @@
     <t>baseline (1) /alternative</t>
   </si>
   <si>
-    <t>Incapacitation and deterrance crime effects of detention, valued by RHV</t>
-  </si>
-  <si>
     <t>Wrongful death damages Social cost of detainment (remove wtp for a human life)</t>
   </si>
   <si>
@@ -489,6 +486,9 @@
   </si>
   <si>
     <t>Denominator Additive component Name</t>
+  </si>
+  <si>
+    <t>Incapacitation and deterrance crime effects of detention</t>
   </si>
 </sst>
 </file>
@@ -544,18 +544,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -571,7 +565,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -585,9 +579,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -964,47 +956,56 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>140</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" t="s">
         <v>141</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" t="s">
         <v>137</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" t="s">
         <v>115</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2">
         <v>2020</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" t="s">
         <v>142</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2">
         <v>12.6</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="11" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="11">
+      <c r="C3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3">
         <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
@@ -1015,7 +1016,7 @@
         <v>134</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1155,7 +1156,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>89</v>
       </c>
@@ -1209,7 +1210,7 @@
         <v>95</v>
       </c>
       <c r="F9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G9">
         <v>2018</v>
@@ -1237,7 +1238,7 @@
         <v>95</v>
       </c>
       <c r="F10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G10">
         <v>2018</v>
@@ -1263,10 +1264,10 @@
         <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I11" s="3">
         <v>0.7</v>
@@ -1289,10 +1290,10 @@
         <v>41</v>
       </c>
       <c r="F12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I12" s="3">
         <v>70</v>
@@ -1329,19 +1330,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="12" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>149</v>
+      <c r="B7" s="11" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/td/PycharmProjects/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AF519A-1F2D-6B49-8894-C1E5E179B313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1056A7-0564-5A48-A2AD-070496E21CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2140" yWindow="-27360" windowWidth="32280" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline components " sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="156">
   <si>
     <t>row_var</t>
   </si>
@@ -488,7 +488,22 @@
     <t>Denominator Additive component Name</t>
   </si>
   <si>
-    <t>Incapacitation and deterrance crime effects of detention</t>
+    <t>Hofflander ( ): Loss of Income Due to Wrongful Death: A Method of Measurement.Insurance Law Journal 1965 Ins. L.J. (1965)  LibGuide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lewbel (2003)l: Calculating compensation in cases of wrongful death. Journal of Econometrics 113, pp 115-128 </t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0304407602001690#SEC2</t>
+  </si>
+  <si>
+    <t>US statistics from https://www.scheuermanlaw.com/wrongful-death-settlement-calculator/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incapacitation and deterrance crime effects of detention measured by Monetary D- bonds </t>
+  </si>
+  <si>
+    <t>D-bond values selected for felony charges</t>
   </si>
 </sst>
 </file>
@@ -499,7 +514,7 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -543,6 +558,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -565,7 +586,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -580,6 +601,10 @@
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -885,12 +910,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{018C5E1B-70FC-CE48-BD0C-84D5CA275194}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="77.6640625" customWidth="1"/>
     <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
@@ -993,7 +1018,7 @@
         <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1004,18 +1029,39 @@
       <c r="F3" t="s">
         <v>115</v>
       </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="I3" s="3">
+        <v>75000</v>
+      </c>
+      <c r="J3" s="3">
+        <v>133685</v>
+      </c>
+      <c r="K3" s="3">
+        <v>75000</v>
+      </c>
+      <c r="L3" t="s">
+        <v>155</v>
+      </c>
+      <c r="M3" t="s">
+        <v>108</v>
+      </c>
+      <c r="N3" t="s">
+        <v>109</v>
+      </c>
+      <c r="O3" t="s">
+        <v>110</v>
+      </c>
+      <c r="P3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="13" t="s">
         <v>145</v>
       </c>
       <c r="D4">
@@ -1031,64 +1077,45 @@
         <v>99</v>
       </c>
       <c r="I4" s="3">
-        <v>973000</v>
+        <v>294728</v>
       </c>
       <c r="J4" s="3">
         <v>100000</v>
       </c>
       <c r="K4" s="3">
-        <v>10000000</v>
+        <v>300000</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="N4" t="s">
-        <v>98</v>
+        <v>152</v>
+      </c>
+      <c r="O4" t="s">
+        <v>150</v>
+      </c>
+      <c r="P4" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5">
-        <v>2022</v>
-      </c>
-      <c r="I5" s="3">
-        <v>11</v>
-      </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="M5" t="s">
-        <v>67</v>
-      </c>
-      <c r="N5" t="s">
-        <v>68</v>
-      </c>
+      <c r="C5" s="7"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
         <v>135</v>
       </c>
       <c r="C6" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
         <v>63</v>
@@ -1097,17 +1124,13 @@
         <v>35</v>
       </c>
       <c r="G6">
-        <v>2021</v>
-      </c>
-      <c r="H6" t="s">
-        <v>72</v>
+        <v>2022</v>
       </c>
       <c r="I6" s="3">
-        <v>295275</v>
-      </c>
-      <c r="K6" s="9">
-        <v>295275</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
       <c r="M6" t="s">
         <v>67</v>
       </c>
@@ -1117,60 +1140,57 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7">
+        <v>2021</v>
+      </c>
+      <c r="H7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="3">
+        <v>295275</v>
+      </c>
+      <c r="K7" s="9">
+        <v>295275</v>
+      </c>
+      <c r="M7" t="s">
+        <v>67</v>
+      </c>
+      <c r="N7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>85</v>
-      </c>
-      <c r="B7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7" t="s">
-        <v>125</v>
-      </c>
-      <c r="F7" t="s">
-        <v>115</v>
-      </c>
-      <c r="G7">
-        <v>2018</v>
-      </c>
-      <c r="I7" s="3">
-        <v>300</v>
-      </c>
-      <c r="J7">
-        <v>200</v>
-      </c>
-      <c r="K7">
-        <v>400</v>
-      </c>
-      <c r="L7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M7" t="s">
-        <v>88</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>89</v>
       </c>
       <c r="B8" t="s">
         <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="F8" t="s">
         <v>115</v>
@@ -1178,58 +1198,71 @@
       <c r="G8">
         <v>2018</v>
       </c>
-      <c r="H8" s="7"/>
       <c r="I8" s="3">
-        <v>448677628</v>
+        <v>300</v>
       </c>
       <c r="J8">
-        <v>448677628</v>
-      </c>
-      <c r="K8" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="K8">
+        <v>400</v>
+      </c>
+      <c r="L8" t="s">
+        <v>87</v>
+      </c>
       <c r="M8" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" t="s">
-        <v>117</v>
+        <v>90</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F9" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="G9">
         <v>2018</v>
       </c>
+      <c r="H9" s="7"/>
       <c r="I9" s="3">
-        <v>33945</v>
-      </c>
-      <c r="J9" s="2"/>
+        <v>448677628</v>
+      </c>
+      <c r="J9">
+        <v>448677628</v>
+      </c>
       <c r="K9" s="2"/>
+      <c r="M9" t="s">
+        <v>131</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
         <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
         <v>117</v>
@@ -1244,50 +1277,52 @@
         <v>2018</v>
       </c>
       <c r="I10" s="3">
-        <v>5171000</v>
-      </c>
+        <v>33945</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s">
         <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
         <v>117</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="F11" t="s">
         <v>146</v>
       </c>
-      <c r="G11" t="s">
-        <v>146</v>
+      <c r="G11">
+        <v>2018</v>
       </c>
       <c r="I11" s="3">
-        <v>0.7</v>
+        <v>5171000</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="B12" t="s">
         <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
         <v>146</v>
@@ -1296,25 +1331,51 @@
         <v>146</v>
       </c>
       <c r="I12" s="3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>146</v>
+      </c>
+      <c r="G13" t="s">
+        <v>146</v>
+      </c>
+      <c r="I13" s="3">
         <v>70</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J13" s="2">
         <v>60.37</v>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" t="s">
+      <c r="K13" s="2"/>
+      <c r="L13" t="s">
         <v>42</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M13" t="s">
         <v>43</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N13" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N7" r:id="rId1" xr:uid="{126C1809-D3C8-9244-9EA2-45648641ED16}"/>
+    <hyperlink ref="N8" r:id="rId1" xr:uid="{126C1809-D3C8-9244-9EA2-45648641ED16}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1836,7 +1897,7 @@
       <c r="O3" t="s">
         <v>21</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="10" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1903,7 +1964,7 @@
       <c r="Q5" t="s">
         <v>101</v>
       </c>
-      <c r="R5" t="s">
+      <c r="R5" s="10" t="s">
         <v>25</v>
       </c>
       <c r="S5" t="s">
@@ -2580,6 +2641,8 @@
   <hyperlinks>
     <hyperlink ref="R19" r:id="rId1" xr:uid="{913DD2C2-09D4-6340-B25B-D342990A3AE8}"/>
     <hyperlink ref="R11" r:id="rId2" xr:uid="{C43FA892-8D61-5549-A0D1-6272414542B3}"/>
+    <hyperlink ref="R5" r:id="rId3" xr:uid="{5D753F69-E906-C04B-9822-C8DAFD369E0A}"/>
+    <hyperlink ref="R3" r:id="rId4" xr:uid="{A8715A40-89FF-2646-97A1-6C834ED4F68F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/td/PycharmProjects/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA1056A7-0564-5A48-A2AD-070496E21CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BCDA39-D4F0-BC46-99ED-455BBD161AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="159">
   <si>
     <t>row_var</t>
   </si>
@@ -504,6 +504,15 @@
   </si>
   <si>
     <t>D-bond values selected for felony charges</t>
+  </si>
+  <si>
+    <t>crime type - felonies selected</t>
+  </si>
+  <si>
+    <t>income</t>
+  </si>
+  <si>
+    <t>Focusing only on the economic losses part in the WDD calculation</t>
   </si>
 </sst>
 </file>
@@ -910,13 +919,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{018C5E1B-70FC-CE48-BD0C-84D5CA275194}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="77.6640625" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" customWidth="1"/>
@@ -931,7 +940,7 @@
     <col min="16" max="16" width="102.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -981,7 +990,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>140</v>
       </c>
@@ -1010,7 +1019,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1029,6 +1038,12 @@
       <c r="F3" t="s">
         <v>115</v>
       </c>
+      <c r="G3">
+        <v>2018</v>
+      </c>
+      <c r="H3" t="s">
+        <v>156</v>
+      </c>
       <c r="I3" s="3">
         <v>75000</v>
       </c>
@@ -1054,7 +1069,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1073,8 +1088,11 @@
       <c r="F4" t="s">
         <v>35</v>
       </c>
+      <c r="G4">
+        <v>2023</v>
+      </c>
       <c r="H4" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="I4" s="3">
         <v>294728</v>
@@ -1085,6 +1103,9 @@
       <c r="K4" s="3">
         <v>300000</v>
       </c>
+      <c r="L4" t="s">
+        <v>158</v>
+      </c>
       <c r="M4" s="12" t="s">
         <v>151</v>
       </c>
@@ -1098,13 +1119,55 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="C5" s="7"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="3">
+        <v>875000</v>
+      </c>
+      <c r="J5" s="3">
+        <v>500000</v>
+      </c>
+      <c r="K5" s="3">
+        <v>875000</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" t="s">
+        <v>100</v>
+      </c>
+      <c r="N5" t="s">
+        <v>101</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="P5" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -1138,7 +1201,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>69</v>
       </c>
@@ -1176,7 +1239,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -1217,7 +1280,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>89</v>
       </c>
@@ -1254,7 +1317,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>92</v>
       </c>
@@ -1282,7 +1345,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -1308,7 +1371,7 @@
         <v>5171000</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>119</v>
       </c>
@@ -1334,7 +1397,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1376,6 +1439,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="N8" r:id="rId1" xr:uid="{126C1809-D3C8-9244-9EA2-45648641ED16}"/>
+    <hyperlink ref="O5" r:id="rId2" xr:uid="{A36DD19A-6484-BA44-A71E-581B1317BD8B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/td/PycharmProjects/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BCDA39-D4F0-BC46-99ED-455BBD161AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA962121-4A3E-0B4C-8557-EBAFBEF4823C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="161">
   <si>
     <t>row_var</t>
   </si>
@@ -513,6 +513,12 @@
   </si>
   <si>
     <t>Focusing only on the economic losses part in the WDD calculation</t>
+  </si>
+  <si>
+    <t>Acute Cost of crime - HAVEN framework (victims)</t>
+  </si>
+  <si>
+    <t>only for violent crimes</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1075,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1127,7 +1133,7 @@
         <v>134</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1138,19 +1144,24 @@
       <c r="F5" t="s">
         <v>35</v>
       </c>
+      <c r="G5">
+        <v>2024</v>
+      </c>
       <c r="H5" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="I5" s="3">
         <v>875000</v>
       </c>
       <c r="J5" s="3">
-        <v>500000</v>
+        <v>10000</v>
       </c>
       <c r="K5" s="3">
         <v>875000</v>
       </c>
-      <c r="L5" s="3"/>
+      <c r="L5" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="M5" t="s">
         <v>100</v>
       </c>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/td/PycharmProjects/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA962121-4A3E-0B4C-8557-EBAFBEF4823C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F776D7A-CE38-6D41-B105-65AEED820DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline components " sheetId="4" r:id="rId1"/>
-    <sheet name="MVPF calculation" sheetId="2" r:id="rId2"/>
+    <sheet name="mvpf_component_mapping" sheetId="5" r:id="rId2"/>
     <sheet name="CCJ Subset Quantification" sheetId="3" r:id="rId3"/>
     <sheet name="OLD Baseline components" sheetId="1" r:id="rId4"/>
   </sheets>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="169">
   <si>
     <t>row_var</t>
   </si>
@@ -473,21 +473,9 @@
     <t>baseline (1) /alternative</t>
   </si>
   <si>
-    <t>Wrongful death damages Social cost of detainment (remove wtp for a human life)</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Numerator Additive component Name</t>
-  </si>
-  <si>
-    <t>component value</t>
-  </si>
-  <si>
-    <t>Denominator Additive component Name</t>
-  </si>
-  <si>
     <t>Hofflander ( ): Loss of Income Due to Wrongful Death: A Method of Measurement.Insurance Law Journal 1965 Ins. L.J. (1965)  LibGuide</t>
   </si>
   <si>
@@ -500,12 +488,6 @@
     <t>US statistics from https://www.scheuermanlaw.com/wrongful-death-settlement-calculator/</t>
   </si>
   <si>
-    <t xml:space="preserve">Incapacitation and deterrance crime effects of detention measured by Monetary D- bonds </t>
-  </si>
-  <si>
-    <t>D-bond values selected for felony charges</t>
-  </si>
-  <si>
     <t>crime type - felonies selected</t>
   </si>
   <si>
@@ -519,6 +501,48 @@
   </si>
   <si>
     <t>only for violent crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incapacitation and deterrance crime effects of detention  </t>
+  </si>
+  <si>
+    <t>Alternatives proven to be ineffecive: D-bond values selected for felony charges</t>
+  </si>
+  <si>
+    <t>Wrongful death damages Social cost of detainment (focusing on economic impact submeasure)</t>
+  </si>
+  <si>
+    <t>baseline</t>
+  </si>
+  <si>
+    <t>no. of criteria</t>
+  </si>
+  <si>
+    <t>govt_refractions</t>
+  </si>
+  <si>
+    <t>govt_health</t>
+  </si>
+  <si>
+    <t>govt_operative</t>
+  </si>
+  <si>
+    <t>soc_community</t>
+  </si>
+  <si>
+    <t>soc_crimeprev</t>
+  </si>
+  <si>
+    <t>soc_court</t>
+  </si>
+  <si>
+    <t>det_rhv</t>
+  </si>
+  <si>
+    <t>det_wtp</t>
+  </si>
+  <si>
+    <t>Scenario</t>
   </si>
 </sst>
 </file>
@@ -601,7 +625,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -615,11 +639,12 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -925,19 +950,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{018C5E1B-70FC-CE48-BD0C-84D5CA275194}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="77.6640625" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="3" max="3" width="58.1640625" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.1640625" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.33203125" customWidth="1"/>
     <col min="12" max="12" width="53.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="72.1640625" bestFit="1" customWidth="1"/>
@@ -1033,7 +1058,7 @@
         <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1048,10 +1073,10 @@
         <v>2018</v>
       </c>
       <c r="H3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I3" s="3">
-        <v>75000</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3">
         <v>133685</v>
@@ -1060,7 +1085,7 @@
         <v>75000</v>
       </c>
       <c r="L3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M3" t="s">
         <v>108</v>
@@ -1075,15 +1100,15 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>145</v>
+      <c r="C4" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1098,7 +1123,7 @@
         <v>2023</v>
       </c>
       <c r="H4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I4" s="3">
         <v>294728</v>
@@ -1110,19 +1135,19 @@
         <v>300000</v>
       </c>
       <c r="L4" t="s">
-        <v>158</v>
-      </c>
-      <c r="M4" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>147</v>
       </c>
       <c r="N4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="O4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="P4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -1133,7 +1158,7 @@
         <v>134</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1148,7 +1173,7 @@
         <v>2024</v>
       </c>
       <c r="H5" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I5" s="3">
         <v>875000</v>
@@ -1160,7 +1185,7 @@
         <v>875000</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="M5" t="s">
         <v>100</v>
@@ -1345,7 +1370,7 @@
         <v>95</v>
       </c>
       <c r="F10" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G10">
         <v>2018</v>
@@ -1373,7 +1398,7 @@
         <v>95</v>
       </c>
       <c r="F11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G11">
         <v>2018</v>
@@ -1399,10 +1424,10 @@
         <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I12" s="3">
         <v>0.7</v>
@@ -1425,10 +1450,10 @@
         <v>41</v>
       </c>
       <c r="F13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I13" s="3">
         <v>70</v>
@@ -1445,6 +1470,12 @@
       </c>
       <c r="N13" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="9:9" x14ac:dyDescent="0.2">
+      <c r="I19">
+        <f>+I9/I10</f>
+        <v>13217.782530564147</v>
       </c>
     </row>
   </sheetData>
@@ -1457,28 +1488,572 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CCEB78A-8117-3143-B4E8-94B34C4CEAC6}">
-  <dimension ref="A1:B7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E4AB0FE-E22E-7046-8B42-84C7BB8E6363}">
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="1" max="1" width="17.5" customWidth="1"/>
+    <col min="2" max="9" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>148</v>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>COUNTIF(B2:I2, 1)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>COUNTIF(B3:I3, 1)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f>COUNTIF(B4:I4, 1)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f>COUNTIF(B5:I5, 1)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <f>COUNTIF(B6:I6, 1)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <f>COUNTIF(B7:I7, 1)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <f>COUNTIF(B8:I8, 1)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <f>COUNTIF(B9:I9, 1)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <f>COUNTIF(B10:I10, 1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <f>COUNTIF(B11:I11, 1)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <f>COUNTIF(B12:I12, 1)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <f>COUNTIF(B13:I13, 1)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <f>COUNTIF(B14:I14, 1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <f>COUNTIF(B15:I15, 1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <f>COUNTIF(B16:I16, 1)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <f>COUNTIF(B17:I17, 1)</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/td/PycharmProjects/CCJ/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F776D7A-CE38-6D41-B105-65AEED820DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F730FF-DE0A-3446-A64B-28624B00AE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline components " sheetId="4" r:id="rId1"/>
-    <sheet name="mvpf_component_mapping" sheetId="5" r:id="rId2"/>
-    <sheet name="CCJ Subset Quantification" sheetId="3" r:id="rId3"/>
-    <sheet name="OLD Baseline components" sheetId="1" r:id="rId4"/>
+    <sheet name="CCJ Subset Quantification" sheetId="3" r:id="rId2"/>
+    <sheet name="OLD Baseline components" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="158">
   <si>
     <t>row_var</t>
   </si>
@@ -488,6 +487,12 @@
     <t>US statistics from https://www.scheuermanlaw.com/wrongful-death-settlement-calculator/</t>
   </si>
   <si>
+    <t xml:space="preserve">Incapacitation and deterrance crime effects of detention measured by Monetary D- bonds </t>
+  </si>
+  <si>
+    <t>D-bond values selected for felony charges</t>
+  </si>
+  <si>
     <t>crime type - felonies selected</t>
   </si>
   <si>
@@ -503,46 +508,7 @@
     <t>only for violent crimes</t>
   </si>
   <si>
-    <t xml:space="preserve">Incapacitation and deterrance crime effects of detention  </t>
-  </si>
-  <si>
-    <t>Alternatives proven to be ineffecive: D-bond values selected for felony charges</t>
-  </si>
-  <si>
-    <t>Wrongful death damages Social cost of detainment (focusing on economic impact submeasure)</t>
-  </si>
-  <si>
-    <t>baseline</t>
-  </si>
-  <si>
-    <t>no. of criteria</t>
-  </si>
-  <si>
-    <t>govt_refractions</t>
-  </si>
-  <si>
-    <t>govt_health</t>
-  </si>
-  <si>
-    <t>govt_operative</t>
-  </si>
-  <si>
-    <t>soc_community</t>
-  </si>
-  <si>
-    <t>soc_crimeprev</t>
-  </si>
-  <si>
-    <t>soc_court</t>
-  </si>
-  <si>
-    <t>det_rhv</t>
-  </si>
-  <si>
-    <t>det_wtp</t>
-  </si>
-  <si>
-    <t>Scenario</t>
+    <t>Wrongful death damages Social cost of detainment (removed wtp for a human life)</t>
   </si>
 </sst>
 </file>
@@ -642,9 +608,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -950,19 +914,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{018C5E1B-70FC-CE48-BD0C-84D5CA275194}">
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.1640625" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="3" max="3" width="77.6640625" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
     <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.6640625" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" customWidth="1"/>
     <col min="11" max="11" width="16.33203125" customWidth="1"/>
     <col min="12" max="12" width="53.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="72.1640625" bestFit="1" customWidth="1"/>
@@ -1058,7 +1022,7 @@
         <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1073,10 +1037,10 @@
         <v>2018</v>
       </c>
       <c r="H3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I3" s="3">
-        <v>0</v>
+        <v>75000</v>
       </c>
       <c r="J3" s="3">
         <v>133685</v>
@@ -1085,7 +1049,7 @@
         <v>75000</v>
       </c>
       <c r="L3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="M3" t="s">
         <v>108</v>
@@ -1100,7 +1064,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1123,7 +1087,7 @@
         <v>2023</v>
       </c>
       <c r="H4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I4" s="3">
         <v>294728</v>
@@ -1135,7 +1099,7 @@
         <v>300000</v>
       </c>
       <c r="L4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M4" s="11" t="s">
         <v>147</v>
@@ -1158,10 +1122,10 @@
         <v>134</v>
       </c>
       <c r="C5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
         <v>126</v>
@@ -1173,7 +1137,7 @@
         <v>2024</v>
       </c>
       <c r="H5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I5" s="3">
         <v>875000</v>
@@ -1185,7 +1149,7 @@
         <v>875000</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M5" t="s">
         <v>100</v>
@@ -1470,12 +1434,6 @@
       </c>
       <c r="N13" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="9:9" x14ac:dyDescent="0.2">
-      <c r="I19">
-        <f>+I9/I10</f>
-        <v>13217.782530564147</v>
       </c>
     </row>
   </sheetData>
@@ -1488,580 +1446,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E4AB0FE-E22E-7046-8B42-84C7BB8E6363}">
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17.5" customWidth="1"/>
-    <col min="2" max="9" width="15.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G1" t="s">
-        <v>162</v>
-      </c>
-      <c r="H1" t="s">
-        <v>161</v>
-      </c>
-      <c r="I1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <f>COUNTIF(B2:I2, 1)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <f>COUNTIF(B3:I3, 1)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <f>COUNTIF(B4:I4, 1)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <f>COUNTIF(B5:I5, 1)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <f>COUNTIF(B6:I6, 1)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <f>COUNTIF(B7:I7, 1)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <f>COUNTIF(B8:I8, 1)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <f>COUNTIF(B9:I9, 1)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <f>COUNTIF(B10:I10, 1)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <f>COUNTIF(B11:I11, 1)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12">
-        <f>COUNTIF(B12:I12, 1)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>1</v>
-      </c>
-      <c r="J13">
-        <f>COUNTIF(B13:I13, 1)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <f>COUNTIF(B14:I14, 1)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <f>COUNTIF(B15:I15, 1)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <f>COUNTIF(B16:I16, 1)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <f>COUNTIF(B17:I17, 1)</f>
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EF59096-85EC-6844-83BB-A3D9FC91749B}">
   <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2394,7 +1778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F730FF-DE0A-3446-A64B-28624B00AE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3843AC4-F107-CF49-A252-0AA55D5D9548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="520" yWindow="4520" windowWidth="26780" windowHeight="12400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline components " sheetId="4" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="160">
   <si>
     <t>row_var</t>
   </si>
@@ -487,12 +487,6 @@
     <t>US statistics from https://www.scheuermanlaw.com/wrongful-death-settlement-calculator/</t>
   </si>
   <si>
-    <t xml:space="preserve">Incapacitation and deterrance crime effects of detention measured by Monetary D- bonds </t>
-  </si>
-  <si>
-    <t>D-bond values selected for felony charges</t>
-  </si>
-  <si>
     <t>crime type - felonies selected</t>
   </si>
   <si>
@@ -508,7 +502,19 @@
     <t>only for violent crimes</t>
   </si>
   <si>
-    <t>Wrongful death damages Social cost of detainment (removed wtp for a human life)</t>
+    <t>Incapacitation and deterrance crime effects of detention (set to 0 re:literature)</t>
+  </si>
+  <si>
+    <t>spillover effects measured by wrongful death damages Social cost of detainment (removed wtp for a human life)</t>
+  </si>
+  <si>
+    <t>https://gregoryeady.com/ResearchMethodsCourse/assets/assignment/Replication_of_Fishbane_et_al.pdf</t>
+  </si>
+  <si>
+    <t>alt_crime_prev_measure</t>
+  </si>
+  <si>
+    <t>alt_wtp_freedom</t>
   </si>
 </sst>
 </file>
@@ -519,7 +525,7 @@
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,7 +570,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <strike/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -591,7 +615,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -605,10 +629,13 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -914,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{018C5E1B-70FC-CE48-BD0C-84D5CA275194}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
@@ -935,7 +962,7 @@
     <col min="16" max="16" width="102.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -985,7 +1012,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>140</v>
       </c>
@@ -1013,8 +1040,11 @@
       <c r="I2">
         <v>12.6</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="M2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1022,7 +1052,7 @@
         <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1030,189 +1060,177 @@
       <c r="E3" t="s">
         <v>137</v>
       </c>
-      <c r="F3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G3">
-        <v>2018</v>
-      </c>
-      <c r="H3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I3" s="3">
-        <v>75000</v>
-      </c>
-      <c r="J3" s="3">
-        <v>133685</v>
-      </c>
-      <c r="K3" s="3">
-        <v>75000</v>
-      </c>
-      <c r="L3" t="s">
-        <v>151</v>
-      </c>
-      <c r="M3" t="s">
-        <v>108</v>
-      </c>
-      <c r="N3" t="s">
-        <v>109</v>
-      </c>
-      <c r="O3" t="s">
-        <v>110</v>
-      </c>
-      <c r="P3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>158</v>
       </c>
       <c r="B4" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>157</v>
+      <c r="C4" t="s">
+        <v>107</v>
       </c>
       <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G4" s="3">
+        <v>2017</v>
+      </c>
+      <c r="I4" s="3">
+        <v>75000</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3">
+        <v>133685</v>
+      </c>
+      <c r="L4" s="3">
+        <v>75000</v>
+      </c>
+      <c r="M4" s="3"/>
+      <c r="O4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>108</v>
+      </c>
+      <c r="R4" t="s">
+        <v>109</v>
+      </c>
+      <c r="S4" t="s">
+        <v>110</v>
+      </c>
+      <c r="T4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" s="11">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F5" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G4">
+      <c r="G5" s="11">
         <v>2023</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H5" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="I5" s="13">
+        <v>294728</v>
+      </c>
+      <c r="J5" s="13">
+        <v>100000</v>
+      </c>
+      <c r="K5" s="13">
+        <v>300000</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="O5" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="P5" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="I4" s="3">
-        <v>294728</v>
-      </c>
-      <c r="J4" s="3">
-        <v>100000</v>
-      </c>
-      <c r="K4" s="3">
-        <v>300000</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="D6" s="11">
+        <v>2</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="11">
+        <v>2024</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="I6" s="13">
+        <v>875000</v>
+      </c>
+      <c r="J6" s="13">
+        <v>10000</v>
+      </c>
+      <c r="K6" s="13">
+        <v>875000</v>
+      </c>
+      <c r="L6" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="M4" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="N4" t="s">
-        <v>148</v>
-      </c>
-      <c r="O4" t="s">
-        <v>146</v>
-      </c>
-      <c r="P4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" t="s">
-        <v>155</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F5" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5">
-        <v>2024</v>
-      </c>
-      <c r="H5" t="s">
-        <v>152</v>
-      </c>
-      <c r="I5" s="3">
-        <v>875000</v>
-      </c>
-      <c r="J5" s="3">
-        <v>10000</v>
-      </c>
-      <c r="K5" s="3">
-        <v>875000</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="M6" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="N5" t="s">
+      <c r="N6" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P6" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="Q6" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6">
-        <v>2022</v>
-      </c>
-      <c r="I6" s="3">
-        <v>11</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="M6" t="s">
-        <v>67</v>
-      </c>
-      <c r="N6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="B7" t="s">
         <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
@@ -1221,17 +1239,13 @@
         <v>35</v>
       </c>
       <c r="G7">
-        <v>2021</v>
-      </c>
-      <c r="H7" t="s">
-        <v>72</v>
+        <v>2022</v>
       </c>
       <c r="I7" s="3">
-        <v>295275</v>
-      </c>
-      <c r="K7" s="9">
-        <v>295275</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
       <c r="M7" t="s">
         <v>67</v>
       </c>
@@ -1239,121 +1253,131 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8">
+        <v>2021</v>
+      </c>
+      <c r="H8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="3">
+        <v>295275</v>
+      </c>
+      <c r="K8" s="9">
+        <v>295275</v>
+      </c>
+      <c r="M8" t="s">
+        <v>67</v>
+      </c>
+      <c r="N8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C9" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D9" s="11">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F9" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G8">
+      <c r="G9" s="11">
         <v>2018</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I9" s="13">
         <v>300</v>
       </c>
-      <c r="J8">
+      <c r="J9" s="11">
         <v>200</v>
       </c>
-      <c r="K8">
+      <c r="K9" s="11">
         <v>400</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L9" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M9" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="N9" s="15" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="10" spans="1:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>89</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>136</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>90</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E10" t="s">
         <v>91</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F10" t="s">
         <v>115</v>
-      </c>
-      <c r="G9">
-        <v>2018</v>
-      </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="3">
-        <v>448677628</v>
-      </c>
-      <c r="J9">
-        <v>448677628</v>
-      </c>
-      <c r="K9" s="2"/>
-      <c r="M9" t="s">
-        <v>131</v>
-      </c>
-      <c r="N9" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>92</v>
-      </c>
-      <c r="B10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" t="s">
-        <v>145</v>
       </c>
       <c r="G10">
         <v>2018</v>
       </c>
+      <c r="H10" s="7"/>
       <c r="I10" s="3">
-        <v>33945</v>
-      </c>
-      <c r="J10" s="2"/>
+        <v>448677628</v>
+      </c>
+      <c r="J10">
+        <v>448677628</v>
+      </c>
       <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="M10" t="s">
+        <v>131</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
         <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
         <v>117</v>
@@ -1368,50 +1392,52 @@
         <v>2018</v>
       </c>
       <c r="I11" s="3">
-        <v>5171000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+        <v>33945</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
         <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
         <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="F12" t="s">
         <v>145</v>
       </c>
-      <c r="G12" t="s">
-        <v>145</v>
+      <c r="G12">
+        <v>2018</v>
       </c>
       <c r="I12" s="3">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+        <v>5171000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="B13" t="s">
         <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
         <v>145</v>
@@ -1420,26 +1446,52 @@
         <v>145</v>
       </c>
       <c r="I13" s="3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" t="s">
+        <v>145</v>
+      </c>
+      <c r="G14" t="s">
+        <v>145</v>
+      </c>
+      <c r="I14" s="3">
         <v>70</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J14" s="2">
         <v>60.37</v>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" t="s">
+      <c r="K14" s="2"/>
+      <c r="L14" t="s">
         <v>42</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M14" t="s">
         <v>43</v>
       </c>
-      <c r="N13" t="s">
+      <c r="N14" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N8" r:id="rId1" xr:uid="{126C1809-D3C8-9244-9EA2-45648641ED16}"/>
-    <hyperlink ref="O5" r:id="rId2" xr:uid="{A36DD19A-6484-BA44-A71E-581B1317BD8B}"/>
+    <hyperlink ref="N9" r:id="rId1" xr:uid="{126C1809-D3C8-9244-9EA2-45648641ED16}"/>
+    <hyperlink ref="O6" r:id="rId2" xr:uid="{A36DD19A-6484-BA44-A71E-581B1317BD8B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/CCJ_quantified_values.xlsx
+++ b/Data/CCJ_quantified_values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/larapesceares/CCJ/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3843AC4-F107-CF49-A252-0AA55D5D9548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329D643F-A378-8141-B99C-D7C0E3165509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="520" yWindow="4520" windowWidth="26780" windowHeight="12400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="440" yWindow="3540" windowWidth="26780" windowHeight="12400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Baseline components " sheetId="4" r:id="rId1"/>
@@ -579,16 +579,15 @@
     </font>
     <font>
       <strike/>
+      <u/>
       <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <strike/>
-      <u/>
       <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -615,7 +614,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -630,12 +629,14 @@
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1116,53 +1117,53 @@
         <v>106</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="11" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:20" s="14" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="14">
         <v>1</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="14">
         <v>2023</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="16">
         <v>294728</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="16">
         <v>100000</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="16">
         <v>300000</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="M5" s="14" t="s">
+      <c r="M5" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="P5" s="11" t="s">
+      <c r="P5" s="14" t="s">
         <v>149</v>
       </c>
     </row>
@@ -1191,16 +1192,16 @@
       <c r="H6" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <v>875000</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <v>10000</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="12">
         <v>875000</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="L6" s="12" t="s">
         <v>154</v>
       </c>
       <c r="M6" s="11" t="s">
@@ -1209,7 +1210,7 @@
       <c r="N6" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="O6" s="15" t="s">
+      <c r="O6" s="13" t="s">
         <v>25</v>
       </c>
       <c r="P6" s="11" t="s">
@@ -1313,7 +1314,7 @@
       <c r="G9" s="11">
         <v>2018</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <v>300</v>
       </c>
       <c r="J9" s="11">
@@ -1328,7 +1329,7 @@
       <c r="M9" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="N9" s="15" t="s">
+      <c r="N9" s="13" t="s">
         <v>129</v>
       </c>
     </row>
